--- a/rapport_compteur.xlsx
+++ b/rapport_compteur.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -46,118 +46,7 @@
     <t xml:space="preserve">Inconnu</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-03-11 00:30:00 +0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-12 00:00:00 +0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-13 00:00:00 +0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-14 00:00:00 +0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-15 00:00:00 +0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-16 00:00:00 +0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-04-30 23:17:35 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-01 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-02 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-03 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-04 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-05 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-06 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-07 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-08 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-09 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-10 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-11 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-12 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-13 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-14 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-15 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-16 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-17 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-18 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-19 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-20 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-21 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-22 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-23 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-24 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-25 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-26 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-27 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-28 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-29 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-30 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-31 00:00:00 +0200</t>
+    <t xml:space="preserve">2025-05-31 08:00:00 +0200</t>
   </si>
   <si>
     <t xml:space="preserve">2025-06-01 00:00:00 +0200</t>
@@ -676,7 +565,115 @@
     <t xml:space="preserve">2025-11-19 00:00:00 +0100</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-11-19 18:28:10 +0100</t>
+    <t xml:space="preserve">2025-11-20 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-21 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-22 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-23 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-24 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-25 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-26 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-27 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-28 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-29 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-30 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-01 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-02 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-03 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-04 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-05 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-06 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-07 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-08 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-09 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-10 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-11 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-12 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-13 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-14 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-15 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-16 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-17 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-18 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-19 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-20 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-21 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-22 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-23 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-24 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-25 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-25 12:36:56 +0100</t>
   </si>
 </sst>
 </file>
@@ -822,7 +819,7 @@
         <v>3521.526</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>78.237</v>
@@ -837,7 +834,7 @@
         <v>1.303</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>1924.316</v>
+        <v>1950.794</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -848,7 +845,7 @@
         <v>3521.526</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>78.237</v>
@@ -863,7 +860,7 @@
         <v>1.303</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>1924.316</v>
+        <v>1950.794</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -874,7 +871,7 @@
         <v>3521.526</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>78.237</v>
@@ -889,7 +886,7 @@
         <v>1.303</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>1924.316</v>
+        <v>1950.794</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -900,7 +897,7 @@
         <v>3521.526</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>78.237</v>
@@ -915,7 +912,7 @@
         <v>1.303</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>1924.316</v>
+        <v>1950.794</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -926,7 +923,7 @@
         <v>3521.526</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>78.237</v>
@@ -941,7 +938,7 @@
         <v>1.303</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>1924.316</v>
+        <v>1950.794</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -952,7 +949,7 @@
         <v>3521.526</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>78.237</v>
@@ -967,7 +964,7 @@
         <v>1.303</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>1924.316</v>
+        <v>1950.794</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -978,7 +975,7 @@
         <v>3521.526</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>78.237</v>
@@ -1004,7 +1001,7 @@
         <v>3521.526</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>78.237</v>
@@ -1030,7 +1027,7 @@
         <v>3521.526</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>78.237</v>
@@ -1056,7 +1053,7 @@
         <v>3521.526</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>78.237</v>
@@ -1082,7 +1079,7 @@
         <v>3521.526</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>78.237</v>
@@ -1108,7 +1105,7 @@
         <v>3521.526</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>78.237</v>
@@ -1134,7 +1131,7 @@
         <v>3521.526</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>78.237</v>
@@ -1160,7 +1157,7 @@
         <v>3521.526</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>78.237</v>
@@ -1186,7 +1183,7 @@
         <v>3521.526</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>78.237</v>
@@ -1212,7 +1209,7 @@
         <v>3521.526</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>78.237</v>
@@ -1238,7 +1235,7 @@
         <v>3521.526</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>78.237</v>
@@ -1264,7 +1261,7 @@
         <v>3521.526</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>78.237</v>
@@ -1290,7 +1287,7 @@
         <v>3521.526</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>78.237</v>
@@ -1316,7 +1313,7 @@
         <v>3521.526</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>78.237</v>
@@ -1342,7 +1339,7 @@
         <v>3521.526</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>78.237</v>
@@ -1368,7 +1365,7 @@
         <v>3521.526</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>78.237</v>
@@ -1394,7 +1391,7 @@
         <v>3521.526</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>78.237</v>
@@ -1420,7 +1417,7 @@
         <v>3521.526</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>212.226</v>
+        <v>212.389</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>78.237</v>
@@ -3055,10 +3052,10 @@
         <v>94</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.551</v>
       </c>
       <c r="C88" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D88" s="0" t="n">
         <v>78.237</v>
@@ -3081,10 +3078,10 @@
         <v>95</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C89" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D89" s="0" t="n">
         <v>78.237</v>
@@ -3107,10 +3104,10 @@
         <v>96</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C90" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D90" s="0" t="n">
         <v>78.237</v>
@@ -3133,10 +3130,10 @@
         <v>97</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C91" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D91" s="0" t="n">
         <v>78.237</v>
@@ -3159,10 +3156,10 @@
         <v>98</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C92" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D92" s="0" t="n">
         <v>78.237</v>
@@ -3185,10 +3182,10 @@
         <v>99</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C93" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D93" s="0" t="n">
         <v>78.237</v>
@@ -3211,10 +3208,10 @@
         <v>100</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C94" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D94" s="0" t="n">
         <v>78.237</v>
@@ -3237,10 +3234,10 @@
         <v>101</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C95" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D95" s="0" t="n">
         <v>78.237</v>
@@ -3263,10 +3260,10 @@
         <v>102</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C96" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D96" s="0" t="n">
         <v>78.237</v>
@@ -3289,10 +3286,10 @@
         <v>103</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C97" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D97" s="0" t="n">
         <v>78.237</v>
@@ -3315,10 +3312,10 @@
         <v>104</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C98" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D98" s="0" t="n">
         <v>78.237</v>
@@ -3341,10 +3338,10 @@
         <v>105</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C99" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D99" s="0" t="n">
         <v>78.237</v>
@@ -3367,10 +3364,10 @@
         <v>106</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C100" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D100" s="0" t="n">
         <v>78.237</v>
@@ -3393,10 +3390,10 @@
         <v>107</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C101" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D101" s="0" t="n">
         <v>78.237</v>
@@ -3419,10 +3416,10 @@
         <v>108</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C102" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D102" s="0" t="n">
         <v>78.237</v>
@@ -3445,10 +3442,10 @@
         <v>109</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C103" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D103" s="0" t="n">
         <v>78.237</v>
@@ -3471,10 +3468,10 @@
         <v>110</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C104" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D104" s="0" t="n">
         <v>78.237</v>
@@ -3497,10 +3494,10 @@
         <v>111</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C105" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D105" s="0" t="n">
         <v>78.237</v>
@@ -3523,10 +3520,10 @@
         <v>112</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C106" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D106" s="0" t="n">
         <v>78.237</v>
@@ -3549,10 +3546,10 @@
         <v>113</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C107" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D107" s="0" t="n">
         <v>78.237</v>
@@ -3575,10 +3572,10 @@
         <v>114</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C108" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D108" s="0" t="n">
         <v>78.237</v>
@@ -3601,10 +3598,10 @@
         <v>115</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C109" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D109" s="0" t="n">
         <v>78.237</v>
@@ -3627,10 +3624,10 @@
         <v>116</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C110" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D110" s="0" t="n">
         <v>78.237</v>
@@ -3653,10 +3650,10 @@
         <v>117</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C111" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D111" s="0" t="n">
         <v>78.237</v>
@@ -3679,10 +3676,10 @@
         <v>118</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C112" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D112" s="0" t="n">
         <v>78.237</v>
@@ -3705,10 +3702,10 @@
         <v>119</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C113" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D113" s="0" t="n">
         <v>78.237</v>
@@ -3731,10 +3728,10 @@
         <v>120</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C114" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D114" s="0" t="n">
         <v>78.237</v>
@@ -3757,10 +3754,10 @@
         <v>121</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C115" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D115" s="0" t="n">
         <v>78.237</v>
@@ -3783,10 +3780,10 @@
         <v>122</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C116" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D116" s="0" t="n">
         <v>78.237</v>
@@ -3809,10 +3806,10 @@
         <v>123</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C117" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D117" s="0" t="n">
         <v>78.237</v>
@@ -3835,10 +3832,10 @@
         <v>124</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C118" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D118" s="0" t="n">
         <v>78.237</v>
@@ -3861,10 +3858,10 @@
         <v>125</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C119" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D119" s="0" t="n">
         <v>78.237</v>
@@ -3887,10 +3884,10 @@
         <v>126</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C120" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D120" s="0" t="n">
         <v>78.237</v>
@@ -3913,10 +3910,10 @@
         <v>127</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C121" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D121" s="0" t="n">
         <v>78.237</v>
@@ -3939,10 +3936,10 @@
         <v>128</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C122" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D122" s="0" t="n">
         <v>78.237</v>
@@ -3965,10 +3962,10 @@
         <v>129</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C123" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D123" s="0" t="n">
         <v>78.237</v>
@@ -3991,10 +3988,10 @@
         <v>130</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C124" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D124" s="0" t="n">
         <v>78.237</v>
@@ -4017,7 +4014,7 @@
         <v>131</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>3521.551</v>
+        <v>3521.565</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>212.432</v>
@@ -5213,7 +5210,7 @@
         <v>177</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>3521.565</v>
+        <v>3522.182</v>
       </c>
       <c r="C171" s="0" t="n">
         <v>212.432</v>
@@ -5239,10 +5236,10 @@
         <v>178</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>3521.565</v>
+        <v>3552.401</v>
       </c>
       <c r="C172" s="0" t="n">
-        <v>212.432</v>
+        <v>212.443</v>
       </c>
       <c r="D172" s="0" t="n">
         <v>78.237</v>
@@ -5265,10 +5262,10 @@
         <v>179</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>3521.565</v>
+        <v>3554.309</v>
       </c>
       <c r="C173" s="0" t="n">
-        <v>212.432</v>
+        <v>212.447</v>
       </c>
       <c r="D173" s="0" t="n">
         <v>78.237</v>
@@ -5291,10 +5288,10 @@
         <v>180</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>3521.565</v>
+        <v>3554.309</v>
       </c>
       <c r="C174" s="0" t="n">
-        <v>212.432</v>
+        <v>212.447</v>
       </c>
       <c r="D174" s="0" t="n">
         <v>78.237</v>
@@ -5317,10 +5314,10 @@
         <v>181</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>3521.565</v>
+        <v>3561.774</v>
       </c>
       <c r="C175" s="0" t="n">
-        <v>212.432</v>
+        <v>212.447</v>
       </c>
       <c r="D175" s="0" t="n">
         <v>78.237</v>
@@ -5343,10 +5340,10 @@
         <v>182</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>3521.565</v>
+        <v>3579.434</v>
       </c>
       <c r="C176" s="0" t="n">
-        <v>212.432</v>
+        <v>212.447</v>
       </c>
       <c r="D176" s="0" t="n">
         <v>78.237</v>
@@ -5369,10 +5366,10 @@
         <v>183</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>3521.565</v>
+        <v>3579.434</v>
       </c>
       <c r="C177" s="0" t="n">
-        <v>212.432</v>
+        <v>212.447</v>
       </c>
       <c r="D177" s="0" t="n">
         <v>78.237</v>
@@ -5395,10 +5392,10 @@
         <v>184</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>3521.565</v>
+        <v>3586.881</v>
       </c>
       <c r="C178" s="0" t="n">
-        <v>212.432</v>
+        <v>212.447</v>
       </c>
       <c r="D178" s="0" t="n">
         <v>78.237</v>
@@ -5421,10 +5418,10 @@
         <v>185</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C179" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D179" s="0" t="n">
         <v>78.237</v>
@@ -5447,10 +5444,10 @@
         <v>186</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C180" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D180" s="0" t="n">
         <v>78.237</v>
@@ -5473,10 +5470,10 @@
         <v>187</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C181" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D181" s="0" t="n">
         <v>78.237</v>
@@ -5499,10 +5496,10 @@
         <v>188</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C182" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D182" s="0" t="n">
         <v>78.237</v>
@@ -5525,10 +5522,10 @@
         <v>189</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C183" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D183" s="0" t="n">
         <v>78.237</v>
@@ -5551,10 +5548,10 @@
         <v>190</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C184" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D184" s="0" t="n">
         <v>78.237</v>
@@ -5577,10 +5574,10 @@
         <v>191</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>3521.565</v>
+        <v>3615.986</v>
       </c>
       <c r="C185" s="0" t="n">
-        <v>212.432</v>
+        <v>212.455</v>
       </c>
       <c r="D185" s="0" t="n">
         <v>78.237</v>
@@ -5603,10 +5600,10 @@
         <v>192</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>3521.565</v>
+        <v>3623.404</v>
       </c>
       <c r="C186" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D186" s="0" t="n">
         <v>78.237</v>
@@ -5629,10 +5626,10 @@
         <v>193</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C187" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D187" s="0" t="n">
         <v>78.237</v>
@@ -5655,10 +5652,10 @@
         <v>194</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C188" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D188" s="0" t="n">
         <v>78.237</v>
@@ -5681,10 +5678,10 @@
         <v>195</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C189" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D189" s="0" t="n">
         <v>78.237</v>
@@ -5707,10 +5704,10 @@
         <v>196</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C190" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D190" s="0" t="n">
         <v>78.237</v>
@@ -5733,10 +5730,10 @@
         <v>197</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C191" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D191" s="0" t="n">
         <v>78.237</v>
@@ -5759,10 +5756,10 @@
         <v>198</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C192" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D192" s="0" t="n">
         <v>78.237</v>
@@ -5785,10 +5782,10 @@
         <v>199</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C193" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D193" s="0" t="n">
         <v>78.237</v>
@@ -5811,10 +5808,10 @@
         <v>200</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>3521.565</v>
+        <v>3626.518</v>
       </c>
       <c r="C194" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D194" s="0" t="n">
         <v>78.237</v>
@@ -5837,10 +5834,10 @@
         <v>201</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>3521.565</v>
+        <v>3627.689</v>
       </c>
       <c r="C195" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D195" s="0" t="n">
         <v>78.237</v>
@@ -5863,10 +5860,10 @@
         <v>202</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>3521.565</v>
+        <v>3627.689</v>
       </c>
       <c r="C196" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D196" s="0" t="n">
         <v>78.237</v>
@@ -5889,10 +5886,10 @@
         <v>203</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>3521.565</v>
+        <v>3627.689</v>
       </c>
       <c r="C197" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D197" s="0" t="n">
         <v>78.237</v>
@@ -5915,10 +5912,10 @@
         <v>204</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>3521.565</v>
+        <v>3627.689</v>
       </c>
       <c r="C198" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D198" s="0" t="n">
         <v>78.237</v>
@@ -5941,10 +5938,10 @@
         <v>205</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>3521.565</v>
+        <v>3627.689</v>
       </c>
       <c r="C199" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D199" s="0" t="n">
         <v>78.237</v>
@@ -5967,10 +5964,10 @@
         <v>206</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>3521.565</v>
+        <v>3627.689</v>
       </c>
       <c r="C200" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D200" s="0" t="n">
         <v>78.237</v>
@@ -5993,10 +5990,10 @@
         <v>207</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>3521.565</v>
+        <v>3628.88</v>
       </c>
       <c r="C201" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D201" s="0" t="n">
         <v>78.237</v>
@@ -6019,10 +6016,10 @@
         <v>208</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>3521.565</v>
+        <v>3628.88</v>
       </c>
       <c r="C202" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D202" s="0" t="n">
         <v>78.237</v>
@@ -6045,10 +6042,10 @@
         <v>209</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>3521.565</v>
+        <v>3628.88</v>
       </c>
       <c r="C203" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D203" s="0" t="n">
         <v>78.237</v>
@@ -6071,10 +6068,10 @@
         <v>210</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>3521.565</v>
+        <v>3628.88</v>
       </c>
       <c r="C204" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D204" s="0" t="n">
         <v>78.237</v>
@@ -6097,10 +6094,10 @@
         <v>211</v>
       </c>
       <c r="B205" s="0" t="n">
-        <v>3521.565</v>
+        <v>3628.88</v>
       </c>
       <c r="C205" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D205" s="0" t="n">
         <v>78.237</v>
@@ -6123,10 +6120,10 @@
         <v>212</v>
       </c>
       <c r="B206" s="0" t="n">
-        <v>3521.565</v>
+        <v>3628.88</v>
       </c>
       <c r="C206" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D206" s="0" t="n">
         <v>78.237</v>
@@ -6149,10 +6146,10 @@
         <v>213</v>
       </c>
       <c r="B207" s="0" t="n">
-        <v>3521.565</v>
+        <v>3629.934</v>
       </c>
       <c r="C207" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D207" s="0" t="n">
         <v>78.237</v>
@@ -6175,10 +6172,10 @@
         <v>214</v>
       </c>
       <c r="B208" s="0" t="n">
-        <v>3522.182</v>
+        <v>3629.934</v>
       </c>
       <c r="C208" s="0" t="n">
-        <v>212.432</v>
+        <v>212.457</v>
       </c>
       <c r="D208" s="0" t="n">
         <v>78.237</v>
@@ -6201,10 +6198,10 @@
         <v>215</v>
       </c>
       <c r="B209" s="0" t="n">
-        <v>3552.401</v>
+        <v>3637.408</v>
       </c>
       <c r="C209" s="0" t="n">
-        <v>212.443</v>
+        <v>212.457</v>
       </c>
       <c r="D209" s="0" t="n">
         <v>78.237</v>
@@ -6227,10 +6224,10 @@
         <v>216</v>
       </c>
       <c r="B210" s="0" t="n">
-        <v>3554.309</v>
+        <v>3646.551</v>
       </c>
       <c r="C210" s="0" t="n">
-        <v>212.447</v>
+        <v>212.457</v>
       </c>
       <c r="D210" s="0" t="n">
         <v>78.237</v>
@@ -6253,10 +6250,10 @@
         <v>217</v>
       </c>
       <c r="B211" s="0" t="n">
-        <v>3554.309</v>
+        <v>3661.745</v>
       </c>
       <c r="C211" s="0" t="n">
-        <v>212.447</v>
+        <v>212.468</v>
       </c>
       <c r="D211" s="0" t="n">
         <v>78.237</v>
@@ -6275,30 +6272,6 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="B212" s="0" t="n">
-        <v>3554.309</v>
-      </c>
-      <c r="C212" s="0" t="n">
-        <v>212.447</v>
-      </c>
-      <c r="D212" s="0" t="n">
-        <v>78.237</v>
-      </c>
-      <c r="E212" s="0" t="n">
-        <v>2.419</v>
-      </c>
-      <c r="F212" s="0" t="n">
-        <v>22.979</v>
-      </c>
-      <c r="G212" s="0" t="n">
-        <v>1.303</v>
-      </c>
-      <c r="H212" s="0" t="n">
-        <v>1950.794</v>
-      </c>
       <c r="I212" s="1"/>
     </row>
   </sheetData>

--- a/rapport_compteur.xlsx
+++ b/rapport_compteur.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="consommations_godfroy" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="consommations_godfroy" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -46,403 +46,7 @@
     <t xml:space="preserve">Inconnu</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-05-31 08:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-01 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-02 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-03 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-04 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-05 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-06 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-07 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-08 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-09 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-10 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-11 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-12 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-13 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-14 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-15 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-16 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-17 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-18 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-19 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-20 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-21 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-22 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-23 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-24 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-25 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-26 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-27 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-28 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-29 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-30 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-01 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-02 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-03 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-04 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-05 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-06 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-07 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-08 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-09 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-10 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-11 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-12 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-13 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-14 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-15 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-16 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-17 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-18 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-19 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-20 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-21 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-22 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-23 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-24 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-25 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-26 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-27 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-28 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-29 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-30 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-31 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-01 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-02 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-03 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-04 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-05 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-06 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-07 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-08 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-09 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-10 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-11 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-12 00:00:01 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-13 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-14 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-15 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-16 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-17 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-18 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-19 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-20 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-21 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-22 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-23 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-24 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-25 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-26 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-27 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-28 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-29 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-30 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-31 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-01 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-02 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-03 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-04 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-05 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-06 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-07 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-08 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-09 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-10 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-11 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-12 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-13 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-14 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-15 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-16 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-17 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-18 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-19 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-20 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-21 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-22 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-23 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-24 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-25 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-26 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-27 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-28 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-29 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-30 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-01 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-02 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-03 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-04 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-05 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-06 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-07 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-08 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-09 00:00:00 +0200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-10 00:00:00 +0200</t>
+    <t xml:space="preserve">2025-10-10 08:00:00 +0200</t>
   </si>
   <si>
     <t xml:space="preserve">2025-10-11 00:00:00 +0200</t>
@@ -673,7 +277,403 @@
     <t xml:space="preserve">2025-12-25 00:00:00 +0100</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-12-25 12:36:56 +0100</t>
+    <t xml:space="preserve">2025-12-26 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-27 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-28 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-29 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-30 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-31 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-01 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-02 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-03 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-04 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-05 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-06 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-07 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-08 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-09 00:00:01 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-10 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-11 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-12 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-13 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-14 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-15 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-16 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-17 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-18 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-19 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-20 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-21 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-22 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-23 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-24 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-25 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-26 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-27 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-28 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-29 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-30 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-31 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-01 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-02 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-03 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-04 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-05 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-06 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-07 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-08 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-09 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-10 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-11 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-12 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-13 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-14 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-15 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-16 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-17 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-18 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-19 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-20 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-21 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-22 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-23 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-24 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-25 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-26 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-27 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-28 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-01 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-02 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-03 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-04 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-05 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-06 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-07 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-08 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-09 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-10 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-11 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-12 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-13 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-14 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-15 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-16 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-17 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-18 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-19 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-20 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-21 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-22 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-23 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-24 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-25 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-26 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-27 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-28 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-29 00:00:00 +0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-30 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-31 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-01 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-02 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-03 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-04 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-05 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-06 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-07 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-08 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-09 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-10 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-11 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-12 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-13 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-14 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-16 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-17 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-18 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-19 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-20 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-21 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-22 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-23 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-24 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-25 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-26 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-27 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-28 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-29 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-30 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-01 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-02 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-03 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-04 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-05 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06 00:00:00 +0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06 14:00:03 +0200</t>
   </si>
 </sst>
 </file>
@@ -769,13 +769,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I212"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.95"/>
@@ -816,10 +922,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>78.237</v>
@@ -842,10 +948,10 @@
         <v>9</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>78.237</v>
@@ -868,10 +974,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>78.237</v>
@@ -894,10 +1000,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>78.237</v>
@@ -920,10 +1026,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>78.237</v>
@@ -946,10 +1052,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>78.237</v>
@@ -972,10 +1078,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>78.237</v>
@@ -998,10 +1104,10 @@
         <v>15</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>78.237</v>
@@ -1024,10 +1130,10 @@
         <v>16</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>78.237</v>
@@ -1050,10 +1156,10 @@
         <v>17</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>78.237</v>
@@ -1076,10 +1182,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>78.237</v>
@@ -1102,10 +1208,10 @@
         <v>19</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>78.237</v>
@@ -1128,10 +1234,10 @@
         <v>20</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>78.237</v>
@@ -1154,10 +1260,10 @@
         <v>21</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>78.237</v>
@@ -1180,10 +1286,10 @@
         <v>22</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>78.237</v>
@@ -1206,10 +1312,10 @@
         <v>23</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>78.237</v>
@@ -1232,10 +1338,10 @@
         <v>24</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>78.237</v>
@@ -1258,10 +1364,10 @@
         <v>25</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>78.237</v>
@@ -1284,10 +1390,10 @@
         <v>26</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>78.237</v>
@@ -1310,10 +1416,10 @@
         <v>27</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>78.237</v>
@@ -1336,10 +1442,10 @@
         <v>28</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>78.237</v>
@@ -1362,10 +1468,10 @@
         <v>29</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>78.237</v>
@@ -1388,10 +1494,10 @@
         <v>30</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>78.237</v>
@@ -1414,10 +1520,10 @@
         <v>31</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>78.237</v>
@@ -1440,10 +1546,10 @@
         <v>32</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>78.237</v>
@@ -1466,10 +1572,10 @@
         <v>33</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>78.237</v>
@@ -1492,10 +1598,10 @@
         <v>34</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>78.237</v>
@@ -1518,10 +1624,10 @@
         <v>35</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>78.237</v>
@@ -1544,10 +1650,10 @@
         <v>36</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>78.237</v>
@@ -1570,10 +1676,10 @@
         <v>37</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>78.237</v>
@@ -1596,10 +1702,10 @@
         <v>38</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>78.237</v>
@@ -1622,10 +1728,10 @@
         <v>39</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>78.237</v>
@@ -1648,10 +1754,10 @@
         <v>40</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C34" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>78.237</v>
@@ -1674,10 +1780,10 @@
         <v>41</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>78.237</v>
@@ -1700,10 +1806,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>78.237</v>
@@ -1726,10 +1832,10 @@
         <v>43</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>78.237</v>
@@ -1752,10 +1858,10 @@
         <v>44</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>3521.526</v>
+        <v>3521.565</v>
       </c>
       <c r="C38" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>78.237</v>
@@ -1778,10 +1884,10 @@
         <v>45</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>3521.526</v>
+        <v>3522.182</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>212.389</v>
+        <v>212.432</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>78.237</v>
@@ -1804,10 +1910,10 @@
         <v>46</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>3521.526</v>
+        <v>3552.401</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>212.389</v>
+        <v>212.443</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>78.237</v>
@@ -1830,10 +1936,10 @@
         <v>47</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>3521.526</v>
+        <v>3554.309</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>212.389</v>
+        <v>212.447</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>78.237</v>
@@ -1856,10 +1962,10 @@
         <v>48</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>3521.526</v>
+        <v>3554.309</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>212.389</v>
+        <v>212.447</v>
       </c>
       <c r="D42" s="0" t="n">
         <v>78.237</v>
@@ -1882,10 +1988,10 @@
         <v>49</v>
       </c>
       <c r="B43" s="0" t="n">
-        <v>3521.526</v>
+        <v>3561.774</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>212.389</v>
+        <v>212.447</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>78.237</v>
@@ -1908,10 +2014,10 @@
         <v>50</v>
       </c>
       <c r="B44" s="0" t="n">
-        <v>3521.526</v>
+        <v>3579.434</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>212.389</v>
+        <v>212.447</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>78.237</v>
@@ -1934,10 +2040,10 @@
         <v>51</v>
       </c>
       <c r="B45" s="0" t="n">
-        <v>3521.526</v>
+        <v>3579.434</v>
       </c>
       <c r="C45" s="0" t="n">
-        <v>212.389</v>
+        <v>212.447</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>78.237</v>
@@ -1960,10 +2066,10 @@
         <v>52</v>
       </c>
       <c r="B46" s="0" t="n">
-        <v>3521.526</v>
+        <v>3586.881</v>
       </c>
       <c r="C46" s="0" t="n">
-        <v>212.389</v>
+        <v>212.447</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>78.237</v>
@@ -1986,10 +2092,10 @@
         <v>53</v>
       </c>
       <c r="B47" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C47" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>78.237</v>
@@ -2012,10 +2118,10 @@
         <v>54</v>
       </c>
       <c r="B48" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C48" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>78.237</v>
@@ -2038,10 +2144,10 @@
         <v>55</v>
       </c>
       <c r="B49" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C49" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>78.237</v>
@@ -2064,10 +2170,10 @@
         <v>56</v>
       </c>
       <c r="B50" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C50" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D50" s="0" t="n">
         <v>78.237</v>
@@ -2090,10 +2196,10 @@
         <v>57</v>
       </c>
       <c r="B51" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C51" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>78.237</v>
@@ -2116,10 +2222,10 @@
         <v>58</v>
       </c>
       <c r="B52" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C52" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>78.237</v>
@@ -2142,10 +2248,10 @@
         <v>59</v>
       </c>
       <c r="B53" s="0" t="n">
-        <v>3521.526</v>
+        <v>3615.986</v>
       </c>
       <c r="C53" s="0" t="n">
-        <v>212.389</v>
+        <v>212.455</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>78.237</v>
@@ -2168,10 +2274,10 @@
         <v>60</v>
       </c>
       <c r="B54" s="0" t="n">
-        <v>3521.526</v>
+        <v>3623.404</v>
       </c>
       <c r="C54" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D54" s="0" t="n">
         <v>78.237</v>
@@ -2194,10 +2300,10 @@
         <v>61</v>
       </c>
       <c r="B55" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C55" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D55" s="0" t="n">
         <v>78.237</v>
@@ -2220,10 +2326,10 @@
         <v>62</v>
       </c>
       <c r="B56" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C56" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D56" s="0" t="n">
         <v>78.237</v>
@@ -2246,10 +2352,10 @@
         <v>63</v>
       </c>
       <c r="B57" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C57" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D57" s="0" t="n">
         <v>78.237</v>
@@ -2272,10 +2378,10 @@
         <v>64</v>
       </c>
       <c r="B58" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C58" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D58" s="0" t="n">
         <v>78.237</v>
@@ -2298,10 +2404,10 @@
         <v>65</v>
       </c>
       <c r="B59" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C59" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D59" s="0" t="n">
         <v>78.237</v>
@@ -2324,10 +2430,10 @@
         <v>66</v>
       </c>
       <c r="B60" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C60" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D60" s="0" t="n">
         <v>78.237</v>
@@ -2350,10 +2456,10 @@
         <v>67</v>
       </c>
       <c r="B61" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C61" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D61" s="0" t="n">
         <v>78.237</v>
@@ -2376,10 +2482,10 @@
         <v>68</v>
       </c>
       <c r="B62" s="0" t="n">
-        <v>3521.526</v>
+        <v>3626.518</v>
       </c>
       <c r="C62" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D62" s="0" t="n">
         <v>78.237</v>
@@ -2402,10 +2508,10 @@
         <v>69</v>
       </c>
       <c r="B63" s="0" t="n">
-        <v>3521.526</v>
+        <v>3627.689</v>
       </c>
       <c r="C63" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D63" s="0" t="n">
         <v>78.237</v>
@@ -2428,10 +2534,10 @@
         <v>70</v>
       </c>
       <c r="B64" s="0" t="n">
-        <v>3521.526</v>
+        <v>3627.689</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D64" s="0" t="n">
         <v>78.237</v>
@@ -2454,10 +2560,10 @@
         <v>71</v>
       </c>
       <c r="B65" s="0" t="n">
-        <v>3521.526</v>
+        <v>3627.689</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D65" s="0" t="n">
         <v>78.237</v>
@@ -2480,10 +2586,10 @@
         <v>72</v>
       </c>
       <c r="B66" s="0" t="n">
-        <v>3521.526</v>
+        <v>3627.689</v>
       </c>
       <c r="C66" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D66" s="0" t="n">
         <v>78.237</v>
@@ -2506,10 +2612,10 @@
         <v>73</v>
       </c>
       <c r="B67" s="0" t="n">
-        <v>3521.526</v>
+        <v>3627.689</v>
       </c>
       <c r="C67" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D67" s="0" t="n">
         <v>78.237</v>
@@ -2532,10 +2638,10 @@
         <v>74</v>
       </c>
       <c r="B68" s="0" t="n">
-        <v>3521.526</v>
+        <v>3627.689</v>
       </c>
       <c r="C68" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D68" s="0" t="n">
         <v>78.237</v>
@@ -2558,10 +2664,10 @@
         <v>75</v>
       </c>
       <c r="B69" s="0" t="n">
-        <v>3521.526</v>
+        <v>3628.88</v>
       </c>
       <c r="C69" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D69" s="0" t="n">
         <v>78.237</v>
@@ -2584,10 +2690,10 @@
         <v>76</v>
       </c>
       <c r="B70" s="0" t="n">
-        <v>3521.526</v>
+        <v>3628.88</v>
       </c>
       <c r="C70" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D70" s="0" t="n">
         <v>78.237</v>
@@ -2610,10 +2716,10 @@
         <v>77</v>
       </c>
       <c r="B71" s="0" t="n">
-        <v>3521.526</v>
+        <v>3628.88</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D71" s="0" t="n">
         <v>78.237</v>
@@ -2636,10 +2742,10 @@
         <v>78</v>
       </c>
       <c r="B72" s="0" t="n">
-        <v>3521.526</v>
+        <v>3628.88</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D72" s="0" t="n">
         <v>78.237</v>
@@ -2662,10 +2768,10 @@
         <v>79</v>
       </c>
       <c r="B73" s="0" t="n">
-        <v>3521.526</v>
+        <v>3628.88</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D73" s="0" t="n">
         <v>78.237</v>
@@ -2688,10 +2794,10 @@
         <v>80</v>
       </c>
       <c r="B74" s="0" t="n">
-        <v>3521.526</v>
+        <v>3628.88</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D74" s="0" t="n">
         <v>78.237</v>
@@ -2714,10 +2820,10 @@
         <v>81</v>
       </c>
       <c r="B75" s="0" t="n">
-        <v>3521.526</v>
+        <v>3629.934</v>
       </c>
       <c r="C75" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D75" s="0" t="n">
         <v>78.237</v>
@@ -2740,10 +2846,10 @@
         <v>82</v>
       </c>
       <c r="B76" s="0" t="n">
-        <v>3521.526</v>
+        <v>3629.934</v>
       </c>
       <c r="C76" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D76" s="0" t="n">
         <v>78.237</v>
@@ -2766,10 +2872,10 @@
         <v>83</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>3521.526</v>
+        <v>3637.408</v>
       </c>
       <c r="C77" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D77" s="0" t="n">
         <v>78.237</v>
@@ -2792,10 +2898,10 @@
         <v>84</v>
       </c>
       <c r="B78" s="0" t="n">
-        <v>3521.526</v>
+        <v>3646.551</v>
       </c>
       <c r="C78" s="0" t="n">
-        <v>212.389</v>
+        <v>212.457</v>
       </c>
       <c r="D78" s="0" t="n">
         <v>78.237</v>
@@ -2818,10 +2924,10 @@
         <v>85</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C79" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D79" s="0" t="n">
         <v>78.237</v>
@@ -2844,10 +2950,10 @@
         <v>86</v>
       </c>
       <c r="B80" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D80" s="0" t="n">
         <v>78.237</v>
@@ -2870,10 +2976,10 @@
         <v>87</v>
       </c>
       <c r="B81" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C81" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D81" s="0" t="n">
         <v>78.237</v>
@@ -2896,10 +3002,10 @@
         <v>88</v>
       </c>
       <c r="B82" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D82" s="0" t="n">
         <v>78.237</v>
@@ -2922,10 +3028,10 @@
         <v>89</v>
       </c>
       <c r="B83" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C83" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D83" s="0" t="n">
         <v>78.237</v>
@@ -2948,10 +3054,10 @@
         <v>90</v>
       </c>
       <c r="B84" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C84" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D84" s="0" t="n">
         <v>78.237</v>
@@ -2974,10 +3080,10 @@
         <v>91</v>
       </c>
       <c r="B85" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C85" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D85" s="0" t="n">
         <v>78.237</v>
@@ -3000,10 +3106,10 @@
         <v>92</v>
       </c>
       <c r="B86" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C86" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D86" s="0" t="n">
         <v>78.237</v>
@@ -3026,10 +3132,10 @@
         <v>93</v>
       </c>
       <c r="B87" s="0" t="n">
-        <v>3521.526</v>
+        <v>3661.745</v>
       </c>
       <c r="C87" s="0" t="n">
-        <v>212.389</v>
+        <v>212.468</v>
       </c>
       <c r="D87" s="0" t="n">
         <v>78.237</v>
@@ -3052,10 +3158,10 @@
         <v>94</v>
       </c>
       <c r="B88" s="0" t="n">
-        <v>3521.551</v>
+        <v>3661.745</v>
       </c>
       <c r="C88" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D88" s="0" t="n">
         <v>78.237</v>
@@ -3078,10 +3184,10 @@
         <v>95</v>
       </c>
       <c r="B89" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C89" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D89" s="0" t="n">
         <v>78.237</v>
@@ -3104,10 +3210,10 @@
         <v>96</v>
       </c>
       <c r="B90" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C90" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D90" s="0" t="n">
         <v>78.237</v>
@@ -3130,10 +3236,10 @@
         <v>97</v>
       </c>
       <c r="B91" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C91" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D91" s="0" t="n">
         <v>78.237</v>
@@ -3156,10 +3262,10 @@
         <v>98</v>
       </c>
       <c r="B92" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C92" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D92" s="0" t="n">
         <v>78.237</v>
@@ -3182,10 +3288,10 @@
         <v>99</v>
       </c>
       <c r="B93" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C93" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D93" s="0" t="n">
         <v>78.237</v>
@@ -3208,10 +3314,10 @@
         <v>100</v>
       </c>
       <c r="B94" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C94" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D94" s="0" t="n">
         <v>78.237</v>
@@ -3234,10 +3340,10 @@
         <v>101</v>
       </c>
       <c r="B95" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C95" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D95" s="0" t="n">
         <v>78.237</v>
@@ -3260,10 +3366,10 @@
         <v>102</v>
       </c>
       <c r="B96" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C96" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D96" s="0" t="n">
         <v>78.237</v>
@@ -3286,10 +3392,10 @@
         <v>103</v>
       </c>
       <c r="B97" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C97" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D97" s="0" t="n">
         <v>78.237</v>
@@ -3312,10 +3418,10 @@
         <v>104</v>
       </c>
       <c r="B98" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C98" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D98" s="0" t="n">
         <v>78.237</v>
@@ -3338,10 +3444,10 @@
         <v>105</v>
       </c>
       <c r="B99" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.745</v>
       </c>
       <c r="C99" s="0" t="n">
-        <v>212.432</v>
+        <v>212.468</v>
       </c>
       <c r="D99" s="0" t="n">
         <v>78.237</v>
@@ -3364,10 +3470,10 @@
         <v>106</v>
       </c>
       <c r="B100" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.772</v>
       </c>
       <c r="C100" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D100" s="0" t="n">
         <v>78.237</v>
@@ -3390,10 +3496,10 @@
         <v>107</v>
       </c>
       <c r="B101" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C101" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D101" s="0" t="n">
         <v>78.237</v>
@@ -3416,10 +3522,10 @@
         <v>108</v>
       </c>
       <c r="B102" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C102" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D102" s="0" t="n">
         <v>78.237</v>
@@ -3442,10 +3548,10 @@
         <v>109</v>
       </c>
       <c r="B103" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C103" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D103" s="0" t="n">
         <v>78.237</v>
@@ -3468,10 +3574,10 @@
         <v>110</v>
       </c>
       <c r="B104" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C104" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D104" s="0" t="n">
         <v>78.237</v>
@@ -3494,10 +3600,10 @@
         <v>111</v>
       </c>
       <c r="B105" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C105" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D105" s="0" t="n">
         <v>78.237</v>
@@ -3520,10 +3626,10 @@
         <v>112</v>
       </c>
       <c r="B106" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C106" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D106" s="0" t="n">
         <v>78.237</v>
@@ -3546,10 +3652,10 @@
         <v>113</v>
       </c>
       <c r="B107" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C107" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D107" s="0" t="n">
         <v>78.237</v>
@@ -3572,10 +3678,10 @@
         <v>114</v>
       </c>
       <c r="B108" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C108" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D108" s="0" t="n">
         <v>78.237</v>
@@ -3598,10 +3704,10 @@
         <v>115</v>
       </c>
       <c r="B109" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C109" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D109" s="0" t="n">
         <v>78.237</v>
@@ -3624,10 +3730,10 @@
         <v>116</v>
       </c>
       <c r="B110" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C110" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D110" s="0" t="n">
         <v>78.237</v>
@@ -3650,10 +3756,10 @@
         <v>117</v>
       </c>
       <c r="B111" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C111" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D111" s="0" t="n">
         <v>78.237</v>
@@ -3676,10 +3782,10 @@
         <v>118</v>
       </c>
       <c r="B112" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C112" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D112" s="0" t="n">
         <v>78.237</v>
@@ -3702,10 +3808,10 @@
         <v>119</v>
       </c>
       <c r="B113" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C113" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D113" s="0" t="n">
         <v>78.237</v>
@@ -3728,10 +3834,10 @@
         <v>120</v>
       </c>
       <c r="B114" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C114" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D114" s="0" t="n">
         <v>78.237</v>
@@ -3754,10 +3860,10 @@
         <v>121</v>
       </c>
       <c r="B115" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C115" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D115" s="0" t="n">
         <v>78.237</v>
@@ -3780,10 +3886,10 @@
         <v>122</v>
       </c>
       <c r="B116" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C116" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D116" s="0" t="n">
         <v>78.237</v>
@@ -3806,10 +3912,10 @@
         <v>123</v>
       </c>
       <c r="B117" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C117" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D117" s="0" t="n">
         <v>78.237</v>
@@ -3832,10 +3938,10 @@
         <v>124</v>
       </c>
       <c r="B118" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C118" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D118" s="0" t="n">
         <v>78.237</v>
@@ -3858,10 +3964,10 @@
         <v>125</v>
       </c>
       <c r="B119" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C119" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D119" s="0" t="n">
         <v>78.237</v>
@@ -3884,10 +3990,10 @@
         <v>126</v>
       </c>
       <c r="B120" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C120" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D120" s="0" t="n">
         <v>78.237</v>
@@ -3910,10 +4016,10 @@
         <v>127</v>
       </c>
       <c r="B121" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C121" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D121" s="0" t="n">
         <v>78.237</v>
@@ -3936,10 +4042,10 @@
         <v>128</v>
       </c>
       <c r="B122" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C122" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D122" s="0" t="n">
         <v>78.237</v>
@@ -3962,10 +4068,10 @@
         <v>129</v>
       </c>
       <c r="B123" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C123" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D123" s="0" t="n">
         <v>78.237</v>
@@ -3988,10 +4094,10 @@
         <v>130</v>
       </c>
       <c r="B124" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C124" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D124" s="0" t="n">
         <v>78.237</v>
@@ -4014,10 +4120,10 @@
         <v>131</v>
       </c>
       <c r="B125" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C125" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D125" s="0" t="n">
         <v>78.237</v>
@@ -4040,10 +4146,10 @@
         <v>132</v>
       </c>
       <c r="B126" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C126" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D126" s="0" t="n">
         <v>78.237</v>
@@ -4066,10 +4172,10 @@
         <v>133</v>
       </c>
       <c r="B127" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C127" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D127" s="0" t="n">
         <v>78.237</v>
@@ -4092,10 +4198,10 @@
         <v>134</v>
       </c>
       <c r="B128" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C128" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D128" s="0" t="n">
         <v>78.237</v>
@@ -4118,10 +4224,10 @@
         <v>135</v>
       </c>
       <c r="B129" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C129" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D129" s="0" t="n">
         <v>78.237</v>
@@ -4144,10 +4250,10 @@
         <v>136</v>
       </c>
       <c r="B130" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C130" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D130" s="0" t="n">
         <v>78.237</v>
@@ -4170,10 +4276,10 @@
         <v>137</v>
       </c>
       <c r="B131" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C131" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D131" s="0" t="n">
         <v>78.237</v>
@@ -4196,10 +4302,10 @@
         <v>138</v>
       </c>
       <c r="B132" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C132" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D132" s="0" t="n">
         <v>78.237</v>
@@ -4222,10 +4328,10 @@
         <v>139</v>
       </c>
       <c r="B133" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C133" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D133" s="0" t="n">
         <v>78.237</v>
@@ -4248,10 +4354,10 @@
         <v>140</v>
       </c>
       <c r="B134" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C134" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D134" s="0" t="n">
         <v>78.237</v>
@@ -4274,10 +4380,10 @@
         <v>141</v>
       </c>
       <c r="B135" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C135" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D135" s="0" t="n">
         <v>78.237</v>
@@ -4300,10 +4406,10 @@
         <v>142</v>
       </c>
       <c r="B136" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C136" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D136" s="0" t="n">
         <v>78.237</v>
@@ -4326,10 +4432,10 @@
         <v>143</v>
       </c>
       <c r="B137" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C137" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D137" s="0" t="n">
         <v>78.237</v>
@@ -4352,10 +4458,10 @@
         <v>144</v>
       </c>
       <c r="B138" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C138" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D138" s="0" t="n">
         <v>78.237</v>
@@ -4378,10 +4484,10 @@
         <v>145</v>
       </c>
       <c r="B139" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C139" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D139" s="0" t="n">
         <v>78.237</v>
@@ -4404,10 +4510,10 @@
         <v>146</v>
       </c>
       <c r="B140" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C140" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D140" s="0" t="n">
         <v>78.237</v>
@@ -4430,10 +4536,10 @@
         <v>147</v>
       </c>
       <c r="B141" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C141" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D141" s="0" t="n">
         <v>78.237</v>
@@ -4456,10 +4562,10 @@
         <v>148</v>
       </c>
       <c r="B142" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C142" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D142" s="0" t="n">
         <v>78.237</v>
@@ -4482,10 +4588,10 @@
         <v>149</v>
       </c>
       <c r="B143" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C143" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D143" s="0" t="n">
         <v>78.237</v>
@@ -4508,10 +4614,10 @@
         <v>150</v>
       </c>
       <c r="B144" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C144" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D144" s="0" t="n">
         <v>78.237</v>
@@ -4534,10 +4640,10 @@
         <v>151</v>
       </c>
       <c r="B145" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C145" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D145" s="0" t="n">
         <v>78.237</v>
@@ -4560,10 +4666,10 @@
         <v>152</v>
       </c>
       <c r="B146" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C146" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D146" s="0" t="n">
         <v>78.237</v>
@@ -4586,10 +4692,10 @@
         <v>153</v>
       </c>
       <c r="B147" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C147" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D147" s="0" t="n">
         <v>78.237</v>
@@ -4612,10 +4718,10 @@
         <v>154</v>
       </c>
       <c r="B148" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C148" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D148" s="0" t="n">
         <v>78.237</v>
@@ -4638,10 +4744,10 @@
         <v>155</v>
       </c>
       <c r="B149" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C149" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D149" s="0" t="n">
         <v>78.237</v>
@@ -4664,10 +4770,10 @@
         <v>156</v>
       </c>
       <c r="B150" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C150" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D150" s="0" t="n">
         <v>78.237</v>
@@ -4690,10 +4796,10 @@
         <v>157</v>
       </c>
       <c r="B151" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C151" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D151" s="0" t="n">
         <v>78.237</v>
@@ -4716,10 +4822,10 @@
         <v>158</v>
       </c>
       <c r="B152" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C152" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D152" s="0" t="n">
         <v>78.237</v>
@@ -4742,10 +4848,10 @@
         <v>159</v>
       </c>
       <c r="B153" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C153" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D153" s="0" t="n">
         <v>78.237</v>
@@ -4768,10 +4874,10 @@
         <v>160</v>
       </c>
       <c r="B154" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C154" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D154" s="0" t="n">
         <v>78.237</v>
@@ -4794,10 +4900,10 @@
         <v>161</v>
       </c>
       <c r="B155" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C155" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D155" s="0" t="n">
         <v>78.237</v>
@@ -4820,10 +4926,10 @@
         <v>162</v>
       </c>
       <c r="B156" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C156" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D156" s="0" t="n">
         <v>78.237</v>
@@ -4846,10 +4952,10 @@
         <v>163</v>
       </c>
       <c r="B157" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C157" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D157" s="0" t="n">
         <v>78.237</v>
@@ -4872,10 +4978,10 @@
         <v>164</v>
       </c>
       <c r="B158" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C158" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D158" s="0" t="n">
         <v>78.237</v>
@@ -4898,10 +5004,10 @@
         <v>165</v>
       </c>
       <c r="B159" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C159" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D159" s="0" t="n">
         <v>78.237</v>
@@ -4924,10 +5030,10 @@
         <v>166</v>
       </c>
       <c r="B160" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C160" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D160" s="0" t="n">
         <v>78.237</v>
@@ -4950,10 +5056,10 @@
         <v>167</v>
       </c>
       <c r="B161" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C161" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D161" s="0" t="n">
         <v>78.237</v>
@@ -4976,10 +5082,10 @@
         <v>168</v>
       </c>
       <c r="B162" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C162" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D162" s="0" t="n">
         <v>78.237</v>
@@ -5002,10 +5108,10 @@
         <v>169</v>
       </c>
       <c r="B163" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C163" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D163" s="0" t="n">
         <v>78.237</v>
@@ -5028,10 +5134,10 @@
         <v>170</v>
       </c>
       <c r="B164" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C164" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D164" s="0" t="n">
         <v>78.237</v>
@@ -5054,10 +5160,10 @@
         <v>171</v>
       </c>
       <c r="B165" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C165" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D165" s="0" t="n">
         <v>78.237</v>
@@ -5080,10 +5186,10 @@
         <v>172</v>
       </c>
       <c r="B166" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C166" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D166" s="0" t="n">
         <v>78.237</v>
@@ -5106,10 +5212,10 @@
         <v>173</v>
       </c>
       <c r="B167" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C167" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D167" s="0" t="n">
         <v>78.237</v>
@@ -5132,10 +5238,10 @@
         <v>174</v>
       </c>
       <c r="B168" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C168" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D168" s="0" t="n">
         <v>78.237</v>
@@ -5158,10 +5264,10 @@
         <v>175</v>
       </c>
       <c r="B169" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C169" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D169" s="0" t="n">
         <v>78.237</v>
@@ -5184,10 +5290,10 @@
         <v>176</v>
       </c>
       <c r="B170" s="0" t="n">
-        <v>3521.565</v>
+        <v>3661.79</v>
       </c>
       <c r="C170" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D170" s="0" t="n">
         <v>78.237</v>
@@ -5210,10 +5316,10 @@
         <v>177</v>
       </c>
       <c r="B171" s="0" t="n">
-        <v>3522.182</v>
+        <v>3661.79</v>
       </c>
       <c r="C171" s="0" t="n">
-        <v>212.432</v>
+        <v>212.538</v>
       </c>
       <c r="D171" s="0" t="n">
         <v>78.237</v>
@@ -5236,10 +5342,10 @@
         <v>178</v>
       </c>
       <c r="B172" s="0" t="n">
-        <v>3552.401</v>
+        <v>3661.79</v>
       </c>
       <c r="C172" s="0" t="n">
-        <v>212.443</v>
+        <v>212.538</v>
       </c>
       <c r="D172" s="0" t="n">
         <v>78.237</v>
@@ -5262,10 +5368,10 @@
         <v>179</v>
       </c>
       <c r="B173" s="0" t="n">
-        <v>3554.309</v>
+        <v>3661.79</v>
       </c>
       <c r="C173" s="0" t="n">
-        <v>212.447</v>
+        <v>212.538</v>
       </c>
       <c r="D173" s="0" t="n">
         <v>78.237</v>
@@ -5288,10 +5394,10 @@
         <v>180</v>
       </c>
       <c r="B174" s="0" t="n">
-        <v>3554.309</v>
+        <v>3661.79</v>
       </c>
       <c r="C174" s="0" t="n">
-        <v>212.447</v>
+        <v>212.538</v>
       </c>
       <c r="D174" s="0" t="n">
         <v>78.237</v>
@@ -5314,10 +5420,10 @@
         <v>181</v>
       </c>
       <c r="B175" s="0" t="n">
-        <v>3561.774</v>
+        <v>3661.79</v>
       </c>
       <c r="C175" s="0" t="n">
-        <v>212.447</v>
+        <v>212.538</v>
       </c>
       <c r="D175" s="0" t="n">
         <v>78.237</v>
@@ -5340,10 +5446,10 @@
         <v>182</v>
       </c>
       <c r="B176" s="0" t="n">
-        <v>3579.434</v>
+        <v>3661.79</v>
       </c>
       <c r="C176" s="0" t="n">
-        <v>212.447</v>
+        <v>212.538</v>
       </c>
       <c r="D176" s="0" t="n">
         <v>78.237</v>
@@ -5366,10 +5472,10 @@
         <v>183</v>
       </c>
       <c r="B177" s="0" t="n">
-        <v>3579.434</v>
+        <v>3661.79</v>
       </c>
       <c r="C177" s="0" t="n">
-        <v>212.447</v>
+        <v>212.538</v>
       </c>
       <c r="D177" s="0" t="n">
         <v>78.237</v>
@@ -5392,10 +5498,10 @@
         <v>184</v>
       </c>
       <c r="B178" s="0" t="n">
-        <v>3586.881</v>
+        <v>3661.79</v>
       </c>
       <c r="C178" s="0" t="n">
-        <v>212.447</v>
+        <v>212.538</v>
       </c>
       <c r="D178" s="0" t="n">
         <v>78.237</v>
@@ -5418,10 +5524,10 @@
         <v>185</v>
       </c>
       <c r="B179" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C179" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D179" s="0" t="n">
         <v>78.237</v>
@@ -5444,10 +5550,10 @@
         <v>186</v>
       </c>
       <c r="B180" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C180" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D180" s="0" t="n">
         <v>78.237</v>
@@ -5470,10 +5576,10 @@
         <v>187</v>
       </c>
       <c r="B181" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C181" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D181" s="0" t="n">
         <v>78.237</v>
@@ -5496,10 +5602,10 @@
         <v>188</v>
       </c>
       <c r="B182" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C182" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D182" s="0" t="n">
         <v>78.237</v>
@@ -5522,10 +5628,10 @@
         <v>189</v>
       </c>
       <c r="B183" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C183" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D183" s="0" t="n">
         <v>78.237</v>
@@ -5548,10 +5654,10 @@
         <v>190</v>
       </c>
       <c r="B184" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C184" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D184" s="0" t="n">
         <v>78.237</v>
@@ -5574,10 +5680,10 @@
         <v>191</v>
       </c>
       <c r="B185" s="0" t="n">
-        <v>3615.986</v>
+        <v>3661.79</v>
       </c>
       <c r="C185" s="0" t="n">
-        <v>212.455</v>
+        <v>212.538</v>
       </c>
       <c r="D185" s="0" t="n">
         <v>78.237</v>
@@ -5600,10 +5706,10 @@
         <v>192</v>
       </c>
       <c r="B186" s="0" t="n">
-        <v>3623.404</v>
+        <v>3661.79</v>
       </c>
       <c r="C186" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D186" s="0" t="n">
         <v>78.237</v>
@@ -5626,10 +5732,10 @@
         <v>193</v>
       </c>
       <c r="B187" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C187" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D187" s="0" t="n">
         <v>78.237</v>
@@ -5652,10 +5758,10 @@
         <v>194</v>
       </c>
       <c r="B188" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C188" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D188" s="0" t="n">
         <v>78.237</v>
@@ -5678,10 +5784,10 @@
         <v>195</v>
       </c>
       <c r="B189" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C189" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D189" s="0" t="n">
         <v>78.237</v>
@@ -5704,10 +5810,10 @@
         <v>196</v>
       </c>
       <c r="B190" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C190" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D190" s="0" t="n">
         <v>78.237</v>
@@ -5730,10 +5836,10 @@
         <v>197</v>
       </c>
       <c r="B191" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C191" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D191" s="0" t="n">
         <v>78.237</v>
@@ -5756,10 +5862,10 @@
         <v>198</v>
       </c>
       <c r="B192" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C192" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D192" s="0" t="n">
         <v>78.237</v>
@@ -5782,10 +5888,10 @@
         <v>199</v>
       </c>
       <c r="B193" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C193" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D193" s="0" t="n">
         <v>78.237</v>
@@ -5808,10 +5914,10 @@
         <v>200</v>
       </c>
       <c r="B194" s="0" t="n">
-        <v>3626.518</v>
+        <v>3661.79</v>
       </c>
       <c r="C194" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D194" s="0" t="n">
         <v>78.237</v>
@@ -5834,10 +5940,10 @@
         <v>201</v>
       </c>
       <c r="B195" s="0" t="n">
-        <v>3627.689</v>
+        <v>3661.79</v>
       </c>
       <c r="C195" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D195" s="0" t="n">
         <v>78.237</v>
@@ -5860,10 +5966,10 @@
         <v>202</v>
       </c>
       <c r="B196" s="0" t="n">
-        <v>3627.689</v>
+        <v>3661.79</v>
       </c>
       <c r="C196" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D196" s="0" t="n">
         <v>78.237</v>
@@ -5886,10 +5992,10 @@
         <v>203</v>
       </c>
       <c r="B197" s="0" t="n">
-        <v>3627.689</v>
+        <v>3661.79</v>
       </c>
       <c r="C197" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D197" s="0" t="n">
         <v>78.237</v>
@@ -5912,10 +6018,10 @@
         <v>204</v>
       </c>
       <c r="B198" s="0" t="n">
-        <v>3627.689</v>
+        <v>3661.79</v>
       </c>
       <c r="C198" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D198" s="0" t="n">
         <v>78.237</v>
@@ -5938,10 +6044,10 @@
         <v>205</v>
       </c>
       <c r="B199" s="0" t="n">
-        <v>3627.689</v>
+        <v>3661.79</v>
       </c>
       <c r="C199" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D199" s="0" t="n">
         <v>78.237</v>
@@ -5964,10 +6070,10 @@
         <v>206</v>
       </c>
       <c r="B200" s="0" t="n">
-        <v>3627.689</v>
+        <v>3661.79</v>
       </c>
       <c r="C200" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D200" s="0" t="n">
         <v>78.237</v>
@@ -5990,10 +6096,10 @@
         <v>207</v>
       </c>
       <c r="B201" s="0" t="n">
-        <v>3628.88</v>
+        <v>3661.79</v>
       </c>
       <c r="C201" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D201" s="0" t="n">
         <v>78.237</v>
@@ -6016,10 +6122,10 @@
         <v>208</v>
       </c>
       <c r="B202" s="0" t="n">
-        <v>3628.88</v>
+        <v>3661.79</v>
       </c>
       <c r="C202" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D202" s="0" t="n">
         <v>78.237</v>
@@ -6042,10 +6148,10 @@
         <v>209</v>
       </c>
       <c r="B203" s="0" t="n">
-        <v>3628.88</v>
+        <v>3661.79</v>
       </c>
       <c r="C203" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D203" s="0" t="n">
         <v>78.237</v>
@@ -6068,10 +6174,10 @@
         <v>210</v>
       </c>
       <c r="B204" s="0" t="n">
-        <v>3628.88</v>
+        <v>3661.79</v>
       </c>
       <c r="C204" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D204" s="0" t="n">
         <v>78.237</v>
@@ -6094,10 +6200,10 @@
         <v>211</v>
       </c>
       <c r="B205" s="0" t="n">
-        <v>3628.88</v>
+        <v>3661.79</v>
       </c>
       <c r="C205" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D205" s="0" t="n">
         <v>78.237</v>
@@ -6120,10 +6226,10 @@
         <v>212</v>
       </c>
       <c r="B206" s="0" t="n">
-        <v>3628.88</v>
+        <v>3661.79</v>
       </c>
       <c r="C206" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D206" s="0" t="n">
         <v>78.237</v>
@@ -6146,10 +6252,10 @@
         <v>213</v>
       </c>
       <c r="B207" s="0" t="n">
-        <v>3629.934</v>
+        <v>3661.79</v>
       </c>
       <c r="C207" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D207" s="0" t="n">
         <v>78.237</v>
@@ -6172,10 +6278,10 @@
         <v>214</v>
       </c>
       <c r="B208" s="0" t="n">
-        <v>3629.934</v>
+        <v>3661.79</v>
       </c>
       <c r="C208" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D208" s="0" t="n">
         <v>78.237</v>
@@ -6198,10 +6304,10 @@
         <v>215</v>
       </c>
       <c r="B209" s="0" t="n">
-        <v>3637.408</v>
+        <v>3661.79</v>
       </c>
       <c r="C209" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D209" s="0" t="n">
         <v>78.237</v>
@@ -6224,10 +6330,10 @@
         <v>216</v>
       </c>
       <c r="B210" s="0" t="n">
-        <v>3646.551</v>
+        <v>3661.79</v>
       </c>
       <c r="C210" s="0" t="n">
-        <v>212.457</v>
+        <v>212.538</v>
       </c>
       <c r="D210" s="0" t="n">
         <v>78.237</v>
@@ -6250,10 +6356,10 @@
         <v>217</v>
       </c>
       <c r="B211" s="0" t="n">
-        <v>3661.745</v>
+        <v>3661.79</v>
       </c>
       <c r="C211" s="0" t="n">
-        <v>212.468</v>
+        <v>212.538</v>
       </c>
       <c r="D211" s="0" t="n">
         <v>78.237</v>
